--- a/tests/testdata/excel/日付1904.xlsx
+++ b/tests/testdata/excel/日付1904.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B14CC98F-70AD-45BB-B914-3896A9DC976F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E50E389-5ACD-4AC5-8C59-2F22786670FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{6D0C9415-F27B-413B-9047-5BA6D7BD1C2B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{8B0CDB39-B3C8-47C6-86ED-64E695924F5C}"/>
   </bookViews>
   <sheets>
     <sheet name="1904" sheetId="1" r:id="rId1"/>
@@ -442,7 +442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1370AFDE-9232-4266-951D-C3FB60DFDE88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EAB6C9-DDD7-4DD5-A1FA-A8CC0B8F23FD}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
